--- a/metalman-auto-engineer/backend/outputs/Tooling_List_92187158.xlsx
+++ b/metalman-auto-engineer/backend/outputs/Tooling_List_92187158.xlsx
@@ -725,6 +725,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -750,6 +753,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -775,6 +781,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -800,6 +809,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1099,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22.36328125" customWidth="1" style="2" min="1" max="1"/>
@@ -1340,7 +1352,7 @@
       </c>
       <c r="L8" s="39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M8" s="48" t="n"/>
@@ -1499,8 +1511,6 @@
     <row r="12" ht="327" customFormat="1" customHeight="1" s="2">
       <c r="C12" s="1" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="L8:N8"/>

--- a/metalman-auto-engineer/backend/outputs/Tooling_List_92187158.xlsx
+++ b/metalman-auto-engineer/backend/outputs/Tooling_List_92187158.xlsx
@@ -711,7 +711,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4476750" cy="4286250"/>
+    <ext cx="4381500" cy="4000500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -725,9 +725,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -739,7 +736,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4476750" cy="4286250"/>
+    <ext cx="4381500" cy="4000500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -753,9 +750,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -767,7 +761,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4476750" cy="4286250"/>
+    <ext cx="4381500" cy="4000500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -781,9 +775,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -795,7 +786,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4476750" cy="4286250"/>
+    <ext cx="4381500" cy="4000500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -809,9 +800,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1111,7 +1099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22.36328125" customWidth="1" style="2" min="1" max="1"/>
@@ -1120,7 +1108,7 @@
     <col width="58.90625" customWidth="1" min="4" max="4"/>
     <col width="31.54296875" customWidth="1" min="5" max="5"/>
     <col width="196.36328125" customWidth="1" min="6" max="6"/>
-    <col width="110.55" customWidth="1" min="7" max="7"/>
+    <col width="115" customWidth="1" min="7" max="7"/>
     <col width="9.54296875" customWidth="1" min="8" max="9"/>
     <col width="21.54296875" customWidth="1" min="10" max="10"/>
     <col width="49.36328125" customWidth="1" min="11" max="11"/>
@@ -1308,7 +1296,7 @@
       <c r="M7" s="48" t="n"/>
       <c r="N7" s="49" t="n"/>
     </row>
-    <row r="8" ht="402" customFormat="1" customHeight="1" s="4">
+    <row r="8" ht="410" customFormat="1" customHeight="1" s="4">
       <c r="A8" s="12" t="n">
         <v>1</v>
       </c>
@@ -1352,13 +1340,13 @@
       </c>
       <c r="L8" s="39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M8" s="48" t="n"/>
       <c r="N8" s="49" t="n"/>
     </row>
-    <row r="9" ht="402" customFormat="1" customHeight="1" s="4">
+    <row r="9" ht="410" customFormat="1" customHeight="1" s="4">
       <c r="A9" s="12" t="n">
         <v>2</v>
       </c>
@@ -1408,7 +1396,7 @@
       <c r="M9" s="48" t="n"/>
       <c r="N9" s="49" t="n"/>
     </row>
-    <row r="10" ht="402" customFormat="1" customHeight="1" s="4">
+    <row r="10" ht="410" customFormat="1" customHeight="1" s="4">
       <c r="A10" s="12" t="n">
         <v>3</v>
       </c>
@@ -1458,7 +1446,7 @@
       <c r="M10" s="48" t="n"/>
       <c r="N10" s="49" t="n"/>
     </row>
-    <row r="11" ht="402" customFormat="1" customHeight="1" s="2" thickBot="1">
+    <row r="11" ht="410" customFormat="1" customHeight="1" s="2" thickBot="1">
       <c r="A11" s="13" t="n">
         <v>4</v>
       </c>
@@ -1511,6 +1499,8 @@
     <row r="12" ht="327" customFormat="1" customHeight="1" s="2">
       <c r="C12" s="1" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="L8:N8"/>
